--- a/TextGame project/Assets/Resources/Story/5.xlsx
+++ b/TextGame project/Assets/Resources/Story/5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382E40E4-A4B1-443D-8AC0-ABC558EAA25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C44012-BDB1-4797-8388-C09DAEE1CEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1045,7 +1045,7 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>48</v>
@@ -1083,7 +1083,7 @@
         <v>4</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" s="3">
         <v>-640.83010000000002</v>
@@ -1106,7 +1106,7 @@
         <v>4</v>
       </c>
       <c r="S5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T5" s="3">
         <v>-640.83010000000002</v>
@@ -1129,7 +1129,7 @@
         <v>4</v>
       </c>
       <c r="S6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T6" s="3">
         <v>-640.83010000000002</v>
@@ -1152,7 +1152,7 @@
         <v>4</v>
       </c>
       <c r="S7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T7" s="3">
         <v>-640.83010000000002</v>
@@ -1175,7 +1175,7 @@
         <v>4</v>
       </c>
       <c r="S8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T8" s="3">
         <v>-640.83010000000002</v>
@@ -1198,7 +1198,7 @@
         <v>4</v>
       </c>
       <c r="S9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T9" s="3">
         <v>-640.83010000000002</v>
@@ -1224,7 +1224,7 @@
         <v>4</v>
       </c>
       <c r="S10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T10" s="3">
         <v>-640.83010000000002</v>
@@ -1247,7 +1247,7 @@
         <v>6</v>
       </c>
       <c r="S11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T11" s="3">
         <v>-640.83010000000002</v>
@@ -1270,7 +1270,7 @@
         <v>6</v>
       </c>
       <c r="S12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T12" s="3">
         <v>-640.83010000000002</v>
@@ -1293,7 +1293,7 @@
         <v>6</v>
       </c>
       <c r="S13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T13" s="3">
         <v>-640.83010000000002</v>
@@ -1316,7 +1316,7 @@
         <v>6</v>
       </c>
       <c r="S14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T14" s="3">
         <v>-640.83010000000002</v>
@@ -1339,7 +1339,7 @@
         <v>6</v>
       </c>
       <c r="S15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T15" s="3">
         <v>-640.83010000000002</v>
@@ -1362,7 +1362,7 @@
         <v>6</v>
       </c>
       <c r="S16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T16" s="3">
         <v>-640.83010000000002</v>
@@ -1385,7 +1385,7 @@
         <v>6</v>
       </c>
       <c r="S17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T17" s="3">
         <v>-640.83010000000002</v>
@@ -1408,7 +1408,7 @@
         <v>6</v>
       </c>
       <c r="S18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T18" s="3">
         <v>-640.83010000000002</v>
@@ -1431,7 +1431,7 @@
         <v>6</v>
       </c>
       <c r="S19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T19" s="3">
         <v>-640.83010000000002</v>
@@ -1454,7 +1454,7 @@
         <v>6</v>
       </c>
       <c r="S20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T20" s="3">
         <v>-640.83010000000002</v>
@@ -1477,7 +1477,7 @@
         <v>6</v>
       </c>
       <c r="S21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T21" s="3">
         <v>-640.83010000000002</v>
@@ -1500,7 +1500,7 @@
         <v>6</v>
       </c>
       <c r="S22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T22" s="3">
         <v>-640.83010000000002</v>
@@ -1523,7 +1523,7 @@
         <v>6</v>
       </c>
       <c r="S23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T23" s="3">
         <v>-640.83010000000002</v>
@@ -1546,7 +1546,7 @@
         <v>6</v>
       </c>
       <c r="S24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T24" s="3">
         <v>-640.83010000000002</v>
@@ -1569,7 +1569,7 @@
         <v>6</v>
       </c>
       <c r="S25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T25" s="3">
         <v>-640.83010000000002</v>
@@ -1592,7 +1592,7 @@
         <v>6</v>
       </c>
       <c r="S26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T26" s="3">
         <v>-640.83010000000002</v>
@@ -1615,7 +1615,7 @@
         <v>6</v>
       </c>
       <c r="S27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T27" s="3">
         <v>-640.83010000000002</v>
@@ -1638,7 +1638,7 @@
         <v>6</v>
       </c>
       <c r="S28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T28" s="3">
         <v>-640.83010000000002</v>
@@ -1661,7 +1661,7 @@
         <v>6</v>
       </c>
       <c r="S29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T29" s="3">
         <v>-640.83010000000002</v>
@@ -1684,7 +1684,7 @@
         <v>6</v>
       </c>
       <c r="S30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T30" s="3">
         <v>-640.83010000000002</v>
@@ -1707,7 +1707,7 @@
         <v>6</v>
       </c>
       <c r="S31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T31" s="3">
         <v>-640.83010000000002</v>
@@ -1730,7 +1730,7 @@
         <v>6</v>
       </c>
       <c r="S32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T32" s="3">
         <v>-640.83010000000002</v>
@@ -1753,7 +1753,7 @@
         <v>6</v>
       </c>
       <c r="S33">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T33" s="3">
         <v>-640.83010000000002</v>
@@ -1776,7 +1776,7 @@
         <v>6</v>
       </c>
       <c r="S34">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T34" s="3">
         <v>-640.83010000000002</v>
@@ -1799,7 +1799,7 @@
         <v>6</v>
       </c>
       <c r="S35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T35" s="3">
         <v>-640.83010000000002</v>
@@ -1822,7 +1822,7 @@
         <v>6</v>
       </c>
       <c r="S36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T36" s="3">
         <v>-640.83010000000002</v>
@@ -1845,7 +1845,7 @@
         <v>6</v>
       </c>
       <c r="S37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T37" s="3">
         <v>-640.83010000000002</v>
@@ -1868,7 +1868,7 @@
         <v>6</v>
       </c>
       <c r="S38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T38" s="3">
         <v>-640.83010000000002</v>
@@ -1891,7 +1891,7 @@
         <v>6</v>
       </c>
       <c r="S39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T39" s="3">
         <v>-640.83010000000002</v>
@@ -1914,7 +1914,7 @@
         <v>6</v>
       </c>
       <c r="S40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T40" s="3">
         <v>-640.83010000000002</v>
@@ -1937,7 +1937,7 @@
         <v>6</v>
       </c>
       <c r="S41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T41" s="3">
         <v>-640.83010000000002</v>
@@ -1960,7 +1960,7 @@
         <v>6</v>
       </c>
       <c r="S42">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T42" s="3">
         <v>-640.83010000000002</v>
@@ -1983,7 +1983,7 @@
         <v>6</v>
       </c>
       <c r="S43">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T43" s="3">
         <v>-640.83010000000002</v>
@@ -2006,7 +2006,7 @@
         <v>6</v>
       </c>
       <c r="S44">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T44" s="3">
         <v>-640.83010000000002</v>
@@ -2029,7 +2029,7 @@
         <v>6</v>
       </c>
       <c r="S45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T45" s="3">
         <v>-640.83010000000002</v>
@@ -2052,7 +2052,7 @@
         <v>6</v>
       </c>
       <c r="S46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T46" s="3">
         <v>-640.83010000000002</v>
@@ -2075,7 +2075,7 @@
         <v>6</v>
       </c>
       <c r="S47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T47" s="3">
         <v>-640.83010000000002</v>
@@ -2098,7 +2098,7 @@
         <v>6</v>
       </c>
       <c r="S48">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T48" s="3">
         <v>-640.83010000000002</v>
@@ -2121,7 +2121,7 @@
         <v>6</v>
       </c>
       <c r="S49">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T49" s="3">
         <v>-640.83010000000002</v>
@@ -2144,7 +2144,7 @@
         <v>6</v>
       </c>
       <c r="S50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T50" s="3">
         <v>-640.83010000000002</v>
@@ -2167,7 +2167,7 @@
         <v>6</v>
       </c>
       <c r="S51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T51" s="3">
         <v>-640.83010000000002</v>
@@ -2190,7 +2190,7 @@
         <v>6</v>
       </c>
       <c r="S52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T52" s="3">
         <v>-640.83010000000002</v>
@@ -2213,7 +2213,7 @@
         <v>6</v>
       </c>
       <c r="S53">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T53" s="3">
         <v>-640.83010000000002</v>
@@ -2236,7 +2236,7 @@
         <v>6</v>
       </c>
       <c r="S54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T54" s="3">
         <v>-640.83010000000002</v>
@@ -2259,7 +2259,7 @@
         <v>6</v>
       </c>
       <c r="S55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T55" s="3">
         <v>-640.83010000000002</v>

--- a/TextGame project/Assets/Resources/Story/5.xlsx
+++ b/TextGame project/Assets/Resources/Story/5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C44012-BDB1-4797-8388-C09DAEE1CEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85014C2-02A9-4F23-AF07-243F831EAB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="88">
   <si>
     <t>Name</t>
   </si>
@@ -241,10 +241,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>（兴奋）你看你看，是旧日记诶！说不定能发现什么秘密！</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>（走过来，皱眉）给我看看。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -322,6 +318,22 @@
   </si>
   <si>
     <t>（压低声音）别出声。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>（兴奋）你看你看，是旧日记！说不定能发现什么秘密！</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -429,7 +441,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -465,6 +477,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1056,8 +1069,8 @@
       <c r="J3" s="3">
         <v>-640.83010000000002</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>26</v>
+      <c r="K3" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>47</v>
@@ -1076,8 +1089,8 @@
       <c r="B4" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
+      <c r="C4" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="R4">
         <v>4</v>
@@ -1122,8 +1135,8 @@
       <c r="B6" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C6" t="s">
-        <v>26</v>
+      <c r="C6" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="R6">
         <v>4</v>
@@ -1168,8 +1181,17 @@
       <c r="B8" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C8" t="s">
-        <v>26</v>
+      <c r="C8" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="3">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="R8">
         <v>4</v>
@@ -1243,6 +1265,15 @@
       <c r="C11" t="s">
         <v>26</v>
       </c>
+      <c r="I11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="3">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="R11">
         <v>6</v>
       </c>
@@ -1378,8 +1409,17 @@
       <c r="B17" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C17" t="s">
-        <v>26</v>
+      <c r="C17" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" s="3">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="R17">
         <v>6</v>
@@ -1473,6 +1513,15 @@
       <c r="C21" t="s">
         <v>26</v>
       </c>
+      <c r="I21" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="R21">
         <v>6</v>
       </c>
@@ -1606,7 +1655,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
         <v>26</v>
@@ -1629,7 +1678,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -1652,7 +1701,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
         <v>26</v>
@@ -1698,7 +1747,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C31" t="s">
         <v>26</v>
@@ -1744,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s">
         <v>26</v>
@@ -1767,7 +1816,7 @@
         <v>25</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
         <v>26</v>
@@ -1790,7 +1839,7 @@
         <v>27</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -1813,10 +1862,19 @@
         <v>25</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" t="s">
-        <v>26</v>
+        <v>69</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J36" s="3">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K36" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="R36">
         <v>6</v>
@@ -1859,10 +1917,19 @@
         <v>25</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C38" t="s">
         <v>26</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J38" s="3">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K38" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="R38">
         <v>6</v>
@@ -1882,7 +1949,7 @@
         <v>27</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C39" t="s">
         <v>28</v>
@@ -1905,7 +1972,7 @@
         <v>25</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C40" t="s">
         <v>26</v>
@@ -1928,7 +1995,7 @@
         <v>27</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C41" t="s">
         <v>28</v>
@@ -1951,10 +2018,19 @@
         <v>25</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" t="s">
-        <v>26</v>
+        <v>75</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J42" s="3">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K42" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="R42">
         <v>6</v>
@@ -1974,7 +2050,7 @@
         <v>27</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C43" t="s">
         <v>28</v>
@@ -1997,10 +2073,19 @@
         <v>25</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C44" t="s">
         <v>26</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J44" s="3">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K44" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="R44">
         <v>6</v>
@@ -2020,7 +2105,7 @@
         <v>27</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C45" t="s">
         <v>28</v>
@@ -2043,10 +2128,19 @@
         <v>25</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" t="s">
-        <v>26</v>
+        <v>79</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J46" s="3">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K46" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="R46">
         <v>6</v>
@@ -2066,7 +2160,7 @@
         <v>27</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C47" t="s">
         <v>28</v>
@@ -2112,10 +2206,10 @@
         <v>25</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" t="s">
-        <v>26</v>
+        <v>81</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="R49">
         <v>6</v>
@@ -2204,10 +2298,10 @@
         <v>25</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C53" t="s">
-        <v>26</v>
+        <v>82</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="R53">
         <v>6</v>
@@ -2250,7 +2344,7 @@
         <v>27</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C55" t="s">
         <v>28</v>
@@ -2282,7 +2376,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A7:A55 A57:A150" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"千叶,旁白,林深"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C112" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7 C9:C16 C18:C35 C37:C41 C43:C45 C47:C48 C50:C52 C54:C112" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Qianye,White,LinShen"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C113:C173" xr:uid="{00000000-0002-0000-0000-000002000000}">
